--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_材料配置表_Dig_MaterialConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/挖坟_材料配置表_Dig_MaterialConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -236,14 +236,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,154 +698,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1200,10 +1196,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
-    <col min="4" max="4" width="26.5" customWidth="1"/>
+    <col min="3" max="3" width="16.6272727272727" customWidth="1"/>
+    <col min="4" max="4" width="33.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="23.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1261,7 +1258,7 @@
       <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
@@ -1278,7 +1275,7 @@
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
@@ -1295,7 +1292,7 @@
       <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
@@ -1312,7 +1309,7 @@
       <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
@@ -1329,7 +1326,7 @@
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
@@ -1346,7 +1343,7 @@
       <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C9" t="s">
@@ -1363,7 +1360,7 @@
       <c r="A10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" t="s">
@@ -1380,7 +1377,7 @@
       <c r="A11" t="s">
         <v>49</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C11" t="s">
@@ -1397,7 +1394,7 @@
       <c r="A12" t="s">
         <v>54</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C12" t="s">
@@ -1414,7 +1411,7 @@
       <c r="A13" t="s">
         <v>59</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C13" t="s">
